--- a/AAII_Financials/Quarterly/ATMV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATMV_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/ATMV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATMV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>ATMV</t>
   </si>
@@ -656,71 +656,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -757,8 +764,14 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -795,8 +808,14 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -833,8 +852,14 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,8 +874,10 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -887,8 +914,14 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,8 +958,14 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -963,8 +1002,14 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1001,8 +1046,14 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1014,8 +1065,10 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1023,7 +1076,7 @@
         <v>200</v>
       </c>
       <c r="E17" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F17" s="3">
         <v>200</v>
@@ -1032,19 +1085,19 @@
         <v>100</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17" s="3">
         <v>0</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
@@ -1052,8 +1105,14 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1061,7 +1120,7 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="F18" s="3">
         <v>-200</v>
@@ -1070,19 +1129,19 @@
         <v>-100</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="I18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J18" s="3">
         <v>0</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
@@ -1090,8 +1149,14 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1106,8 +1171,10 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1115,28 +1182,28 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1144,8 +1211,14 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1153,28 +1226,28 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>800</v>
+      </c>
+      <c r="G21" s="3">
         <v>700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>600</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
+      <c r="J21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
+      <c r="L21" s="3">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
@@ -1182,8 +1255,14 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1220,37 +1299,43 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>300</v>
+      </c>
+      <c r="E23" s="3">
         <v>800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
+        <v>800</v>
+      </c>
+      <c r="G23" s="3">
         <v>700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>600</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
         <v>0</v>
       </c>
       <c r="J23" s="3">
         <v>0</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
+      <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
@@ -1258,8 +1343,14 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1296,8 +1387,14 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1334,37 +1431,43 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>300</v>
+      </c>
+      <c r="E26" s="3">
         <v>800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
+        <v>800</v>
+      </c>
+      <c r="G26" s="3">
         <v>700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>600</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
         <v>0</v>
       </c>
       <c r="J26" s="3">
         <v>0</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
@@ -1372,37 +1475,43 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>300</v>
+      </c>
+      <c r="E27" s="3">
         <v>800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
+        <v>800</v>
+      </c>
+      <c r="G27" s="3">
         <v>700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>600</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
         <v>0</v>
       </c>
       <c r="J27" s="3">
         <v>0</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
@@ -1410,8 +1519,14 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1448,8 +1563,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1486,8 +1607,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1524,8 +1651,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1562,8 +1695,14 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1571,28 +1710,28 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1600,37 +1739,43 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>300</v>
+      </c>
+      <c r="E33" s="3">
         <v>800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
+        <v>800</v>
+      </c>
+      <c r="G33" s="3">
         <v>700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>600</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
         <v>0</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
+      <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
+        <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
@@ -1638,8 +1783,14 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1676,37 +1827,43 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>300</v>
+      </c>
+      <c r="E35" s="3">
         <v>800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
+        <v>800</v>
+      </c>
+      <c r="G35" s="3">
         <v>700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>600</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
         <v>0</v>
       </c>
       <c r="J35" s="3">
         <v>0</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
+      <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
+        <v>0</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
@@ -1714,51 +1871,63 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1773,8 +1942,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1789,31 +1960,33 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>700</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+      <c r="J41" s="3">
+        <v>0</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1827,8 +2000,14 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1865,8 +2044,14 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1882,14 +2067,14 @@
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3">
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1903,8 +2088,14 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1941,32 +2132,38 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
       </c>
       <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1979,8 +2176,14 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1988,22 +2191,22 @@
         <v>100</v>
       </c>
       <c r="E46" s="3">
+        <v>100</v>
+      </c>
+      <c r="F46" s="3">
+        <v>100</v>
+      </c>
+      <c r="G46" s="3">
         <v>300</v>
-      </c>
-      <c r="F46" s="3">
-        <v>400</v>
-      </c>
-      <c r="G46" s="3">
-        <v>700</v>
       </c>
       <c r="H46" s="3">
         <v>400</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+      <c r="I46" s="3">
+        <v>700</v>
+      </c>
+      <c r="J46" s="3">
+        <v>400</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2017,29 +2220,35 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>50900</v>
+      </c>
+      <c r="F47" s="3">
         <v>73000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>72100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>71200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>70400</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2055,8 +2264,14 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2093,8 +2308,14 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2131,8 +2352,14 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2169,8 +2396,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2207,16 +2440,22 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -2224,11 +2463,11 @@
       <c r="G52" s="3">
         <v>0</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2245,8 +2484,14 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2283,32 +2528,38 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>50900</v>
+      </c>
+      <c r="F54" s="3">
         <v>73100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>72300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>71600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>71200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>400</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2321,8 +2572,14 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2337,8 +2594,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2353,32 +2612,34 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>200</v>
+      </c>
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
       <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2391,31 +2652,37 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2429,8 +2696,14 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2447,14 +2720,14 @@
         <v>0</v>
       </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2467,32 +2740,38 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>400</v>
+      </c>
+      <c r="F60" s="3">
         <v>100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>100</v>
       </c>
-      <c r="F60" s="3">
-        <v>0</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
         <v>300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>300</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,8 +2784,14 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2543,8 +2828,14 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2581,8 +2872,14 @@
       <c r="N62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2619,8 +2916,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2657,8 +2960,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2695,32 +3004,38 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>400</v>
+      </c>
+      <c r="F66" s="3">
         <v>100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>100</v>
       </c>
-      <c r="F66" s="3">
-        <v>0</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3">
         <v>300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>300</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2733,8 +3048,14 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2749,8 +3070,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2787,8 +3110,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2825,8 +3154,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2863,8 +3198,14 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2901,31 +3242,37 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="E72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3">
         <v>200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>400</v>
       </c>
-      <c r="G72" s="3">
-        <v>0</v>
-      </c>
-      <c r="H72" s="3">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+      <c r="I72" s="3">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3">
+        <v>0</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2939,8 +3286,14 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2977,8 +3330,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3015,8 +3374,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3053,31 +3418,37 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>50600</v>
+      </c>
+      <c r="F76" s="3">
         <v>73000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>72300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>71600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>70900</v>
       </c>
-      <c r="H76" s="3">
-        <v>0</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+      <c r="J76" s="3">
+        <v>0</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3091,8 +3462,14 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3129,80 +3506,92 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>300</v>
+      </c>
+      <c r="E81" s="3">
         <v>800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
+        <v>800</v>
+      </c>
+      <c r="G81" s="3">
         <v>700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>600</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
         <v>0</v>
       </c>
       <c r="J81" s="3">
         <v>0</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
+      <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
+        <v>0</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
@@ -3210,8 +3599,14 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3226,8 +3621,10 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3264,8 +3661,14 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3302,8 +3705,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3340,8 +3749,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3378,8 +3793,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3416,8 +3837,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3454,46 +3881,58 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>-200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
       <c r="I89" s="3">
         <v>0</v>
       </c>
       <c r="J89" s="3">
         <v>0</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
+      <c r="K89" s="3">
+        <v>0</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3508,8 +3947,10 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3546,8 +3987,14 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3584,8 +4031,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3622,31 +4075,37 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -3660,8 +4119,14 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3676,8 +4141,10 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3714,8 +4181,14 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3752,8 +4225,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3790,8 +4269,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3828,31 +4313,37 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -3866,8 +4357,14 @@
       <c r="N100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3904,42 +4401,54 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>700</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ATMV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATMV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>ATMV</t>
   </si>
@@ -656,67 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -726,8 +727,11 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -770,8 +774,11 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -814,8 +821,11 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -858,8 +868,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,8 +889,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -920,8 +934,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,8 +981,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1008,8 +1028,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1052,8 +1075,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1067,13 +1093,14 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E17" s="3">
         <v>200</v>
@@ -1082,25 +1109,25 @@
         <v>200</v>
       </c>
       <c r="G17" s="3">
+        <v>200</v>
+      </c>
+      <c r="H17" s="3">
         <v>100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>100</v>
       </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
       <c r="K17" s="3">
         <v>0</v>
       </c>
       <c r="L17" s="3">
         <v>0</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
+      <c r="M17" s="3">
+        <v>0</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
@@ -1111,8 +1138,11 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1126,25 +1156,25 @@
         <v>-200</v>
       </c>
       <c r="G18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-100</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
       <c r="K18" s="3">
         <v>0</v>
       </c>
       <c r="L18" s="3">
         <v>0</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
+      <c r="M18" s="3">
+        <v>0</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
@@ -1155,8 +1185,11 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1173,8 +1206,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1182,19 +1216,19 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="F20" s="3">
         <v>1000</v>
       </c>
       <c r="G20" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H20" s="3">
         <v>800</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1205,8 +1239,8 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1217,8 +1251,11 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1226,31 +1263,31 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="F21" s="3">
         <v>800</v>
       </c>
       <c r="G21" s="3">
+        <v>800</v>
+      </c>
+      <c r="H21" s="3">
         <v>700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>600</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
@@ -1261,8 +1298,11 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1305,29 +1345,32 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>400</v>
+      </c>
+      <c r="E23" s="3">
         <v>300</v>
-      </c>
-      <c r="E23" s="3">
-        <v>800</v>
       </c>
       <c r="F23" s="3">
         <v>800</v>
       </c>
       <c r="G23" s="3">
+        <v>800</v>
+      </c>
+      <c r="H23" s="3">
         <v>700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>600</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
         <v>0</v>
       </c>
@@ -1337,8 +1380,8 @@
       <c r="L23" s="3">
         <v>0</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
+      <c r="M23" s="3">
+        <v>0</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
@@ -1349,8 +1392,11 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1393,8 +1439,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1437,29 +1486,32 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>400</v>
+      </c>
+      <c r="E26" s="3">
         <v>300</v>
-      </c>
-      <c r="E26" s="3">
-        <v>800</v>
       </c>
       <c r="F26" s="3">
         <v>800</v>
       </c>
       <c r="G26" s="3">
+        <v>800</v>
+      </c>
+      <c r="H26" s="3">
         <v>700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>600</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
       <c r="J26" s="3">
         <v>0</v>
       </c>
@@ -1469,8 +1521,8 @@
       <c r="L26" s="3">
         <v>0</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
+      <c r="M26" s="3">
+        <v>0</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
@@ -1481,29 +1533,32 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>400</v>
+      </c>
+      <c r="E27" s="3">
         <v>300</v>
-      </c>
-      <c r="E27" s="3">
-        <v>800</v>
       </c>
       <c r="F27" s="3">
         <v>800</v>
       </c>
       <c r="G27" s="3">
+        <v>800</v>
+      </c>
+      <c r="H27" s="3">
         <v>700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>600</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
         <v>0</v>
       </c>
@@ -1513,8 +1568,8 @@
       <c r="L27" s="3">
         <v>0</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
+      <c r="M27" s="3">
+        <v>0</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
@@ -1525,8 +1580,11 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1569,8 +1627,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1674,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1657,8 +1721,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1701,8 +1768,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1710,19 +1780,19 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
       <c r="F32" s="3">
         <v>-1000</v>
       </c>
       <c r="G32" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="H32" s="3">
         <v>-800</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -1733,8 +1803,8 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1745,29 +1815,32 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>400</v>
+      </c>
+      <c r="E33" s="3">
         <v>300</v>
-      </c>
-      <c r="E33" s="3">
-        <v>800</v>
       </c>
       <c r="F33" s="3">
         <v>800</v>
       </c>
       <c r="G33" s="3">
+        <v>800</v>
+      </c>
+      <c r="H33" s="3">
         <v>700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>600</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
         <v>0</v>
       </c>
@@ -1777,8 +1850,8 @@
       <c r="L33" s="3">
         <v>0</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
+      <c r="M33" s="3">
+        <v>0</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
@@ -1789,8 +1862,11 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1833,29 +1909,32 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>400</v>
+      </c>
+      <c r="E35" s="3">
         <v>300</v>
-      </c>
-      <c r="E35" s="3">
-        <v>800</v>
       </c>
       <c r="F35" s="3">
         <v>800</v>
       </c>
       <c r="G35" s="3">
+        <v>800</v>
+      </c>
+      <c r="H35" s="3">
         <v>700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>600</v>
       </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
         <v>0</v>
       </c>
@@ -1865,8 +1944,8 @@
       <c r="L35" s="3">
         <v>0</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
+      <c r="M35" s="3">
+        <v>0</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
@@ -1877,46 +1956,49 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1926,8 +2008,11 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1944,8 +2029,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1962,8 +2048,9 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1974,22 +2061,22 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>700</v>
       </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
+      <c r="K41" s="3">
+        <v>0</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
@@ -2006,8 +2093,11 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2050,8 +2140,11 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2073,11 +2166,11 @@
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
@@ -2094,8 +2187,11 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2138,8 +2234,11 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2147,7 +2246,7 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
@@ -2156,17 +2255,17 @@
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I45" s="3">
         <v>100</v>
       </c>
       <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,8 +2281,11 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2197,20 +2299,20 @@
         <v>100</v>
       </c>
       <c r="G46" s="3">
+        <v>100</v>
+      </c>
+      <c r="H46" s="3">
         <v>300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>400</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2226,32 +2328,35 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E47" s="3">
         <v>51500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>50900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>73000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>72100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>71200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>70400</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2270,8 +2375,11 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2314,8 +2422,11 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2358,8 +2469,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2402,8 +2516,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2446,19 +2563,22 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -2469,8 +2589,8 @@
       <c r="I52" s="3">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2490,8 +2610,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2534,35 +2657,38 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E54" s="3">
         <v>51600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>50900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>73100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>72300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>71600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>71200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>400</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2578,8 +2704,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2596,8 +2725,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2614,8 +2744,9 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2623,26 +2754,26 @@
         <v>400</v>
       </c>
       <c r="E57" s="3">
+        <v>400</v>
+      </c>
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
       <c r="H57" s="3">
         <v>0</v>
       </c>
       <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2658,20 +2789,23 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>200</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2684,8 +2818,8 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2702,8 +2836,11 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2726,11 +2863,11 @@
         <v>0</v>
       </c>
       <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2746,34 +2883,37 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>900</v>
+      </c>
+      <c r="E60" s="3">
         <v>700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>400</v>
-      </c>
-      <c r="F60" s="3">
-        <v>100</v>
       </c>
       <c r="G60" s="3">
         <v>100</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I60" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3">
         <v>300</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
+      <c r="K60" s="3">
+        <v>300</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
@@ -2790,8 +2930,11 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2834,8 +2977,11 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2878,8 +3024,11 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2922,8 +3071,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2966,8 +3118,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3010,34 +3165,37 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>900</v>
+      </c>
+      <c r="E66" s="3">
         <v>700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>400</v>
-      </c>
-      <c r="F66" s="3">
-        <v>100</v>
       </c>
       <c r="G66" s="3">
         <v>100</v>
       </c>
       <c r="H66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I66" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J66" s="3">
         <v>300</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
+      <c r="K66" s="3">
+        <v>300</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
@@ -3054,8 +3212,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3072,8 +3233,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3116,8 +3278,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3160,8 +3325,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3204,8 +3372,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3248,34 +3419,37 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-300</v>
       </c>
-      <c r="F72" s="3">
-        <v>0</v>
-      </c>
       <c r="G72" s="3">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3">
         <v>200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>400</v>
       </c>
-      <c r="I72" s="3">
-        <v>0</v>
-      </c>
       <c r="J72" s="3">
         <v>0</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
+      <c r="K72" s="3">
+        <v>0</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
@@ -3292,8 +3466,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3336,8 +3513,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3380,8 +3560,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3424,34 +3607,37 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51300</v>
+      </c>
+      <c r="E76" s="3">
         <v>50900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>50600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>73000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>72300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>71600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>70900</v>
       </c>
-      <c r="J76" s="3">
-        <v>0</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
+      <c r="K76" s="3">
+        <v>0</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
@@ -3468,8 +3654,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3512,46 +3701,49 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3561,29 +3753,32 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>400</v>
+      </c>
+      <c r="E81" s="3">
         <v>300</v>
-      </c>
-      <c r="E81" s="3">
-        <v>800</v>
       </c>
       <c r="F81" s="3">
         <v>800</v>
       </c>
       <c r="G81" s="3">
+        <v>800</v>
+      </c>
+      <c r="H81" s="3">
         <v>700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>600</v>
       </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
         <v>0</v>
       </c>
@@ -3593,8 +3788,8 @@
       <c r="L81" s="3">
         <v>0</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
+      <c r="M81" s="3">
+        <v>0</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
@@ -3605,8 +3800,11 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3623,8 +3821,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3667,8 +3866,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3711,8 +3913,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3755,8 +3960,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3799,8 +4007,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3843,8 +4054,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3887,8 +4101,11 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3899,17 +4116,17 @@
         <v>0</v>
       </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>-200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
         <v>0</v>
       </c>
@@ -3919,11 +4136,11 @@
       <c r="L89" s="3">
         <v>0</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O89" s="3">
         <v>0</v>
@@ -3931,8 +4148,11 @@
       <c r="P89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3949,8 +4169,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3993,8 +4214,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4037,8 +4261,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4081,16 +4308,19 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+      <c r="E94" s="3">
+        <v>-100</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -4107,8 +4337,8 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -4125,8 +4355,11 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4143,8 +4376,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4187,8 +4421,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4231,8 +4468,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4275,8 +4515,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4319,16 +4562,19 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
+      <c r="E100" s="3">
+        <v>100</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
@@ -4345,8 +4591,8 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -4363,8 +4609,11 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4407,8 +4656,11 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4419,28 +4671,28 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>700</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
@@ -4449,6 +4701,9 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
